--- a/stories/arbres/ATOM-SAN.ECR.001-01.xlsx
+++ b/stories/arbres/ATOM-SAN.ECR.001-01.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Maya est dans le salon. Elle regarde un dessin à l'écran. Les couleurs dansent. Maman s'assoit près d'elle. Maman dit : fini. L'adulte dit fini. Maya écoute. Elle va éteindre. Maya éteint l'écran. L'écran devient noir. Elle pose la télécommande. Maman dit : on prend un autre jeu. Maya va choisir un jeu. Elle choisit les cubes en bois. Elles construisent une tour. La tour est haute. Maya dit : l'écran est éteint. Un autre jeu, c'est bien. Maman tape dans ses mains. Maya rit. Elles ajoutent un toit. Puis elles rangent les cubes. Maya a éteint. Elle a choisi un autre jeu.</t>
+          <t>Maya est dans le salon. Elle regarde un dessin à l'écran. Les couleurs dansent. Maman s'assoit près d'elle. Fini. L'adulte dit fini. Maya écoute. Elle va éteindre. Maya éteint l'écran. L'écran devient noir. Elle pose la télécommande. On prend un autre jeu. Maya va choisir un jeu. Elle choisit les cubes en bois. Elles construisent une tour. La tour est haute. L'écran est éteint. Un autre jeu, c'est bien. Maman tape dans ses mains. Maya rit. Elles ajoutent un toit. Puis elles rangent les cubes. Maya a éteint. Elle a choisi un autre jeu.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,17 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Maya est dans le salon. Elle regarde un dessin à l'écran. Les couleurs dansent. Maman s'assoit près d'elle.
+maman|Fini. L'adulte dit fini.
+narrateur|Maya écoute. Elle va éteindre. Maya éteint l'écran. L'écran devient noir. Elle pose la télécommande.
+maman|On prend un autre jeu.
+narrateur|Maya va choisir un jeu. Elle choisit les cubes en bois. Elles construisent une tour. La tour est haute.
+enfant-f|L'écran est éteint.
+narrateur|Un autre jeu, c'est bien. Maman tape dans ses mains. Maya rit. Elles ajoutent un toit. Puis elles rangent les cubes. Maya a éteint. Elle a choisi un autre jeu.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1492,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Maman dit fini. Que fait Maya ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1665,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Maman a dit fini. Maya a éteint. Elle a pris un autre jeu. Les cubes, c'était bien.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1828,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|La tour reste un moment. Maya dit merci à maman. Le salon est calme.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1995,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2018,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2035,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.ECR.001-01.xlsx
+++ b/stories/arbres/ATOM-SAN.ECR.001-01.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1316,6 +1321,7 @@
 narrateur|Un autre jeu, c'est bien. Maman tape dans ses mains. Maya rit. Elles ajoutent un toit. Puis elles rangent les cubes. Maya a éteint. Elle a choisi un autre jeu.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1499,6 +1505,7 @@
           <t>narrateur|Maman dit fini. Que fait Maya ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1670,6 +1677,7 @@
           <t>narrateur|Maman a dit fini. Maya a éteint. Elle a pris un autre jeu. Les cubes, c'était bien.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1833,6 +1841,7 @@
           <t>narrateur|La tour reste un moment. Maya dit merci à maman. Le salon est calme.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2000,6 +2009,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2018,7 +2028,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2042,6 +2052,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2056,7 +2080,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2243,6 +2267,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SAN.ECR.001-01.xlsx
+++ b/stories/arbres/ATOM-SAN.ECR.001-01.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Maya éteint l'écran</t>
+          <t>La tour après l'écran</t>
         </is>
       </c>
     </row>
@@ -602,6 +602,7 @@
           <t>secondary_lessons</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -830,6 +831,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>La lampe est allumée. Le rideau est couleur miel. Maman dit fini. Nina éteint. Elles bâtissent une tour de cubes.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1185,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Maya est dans le salon. Elle regarde un dessin à l'écran. Les couleurs dansent. Maman s'assoit près d'elle. Fini. L'adulte dit fini. Maya écoute. Elle va éteindre. Maya éteint l'écran. L'écran devient noir. Elle pose la télécommande. On prend un autre jeu. Maya va choisir un jeu. Elle choisit les cubes en bois. Elles construisent une tour. La tour est haute. L'écran est éteint. Un autre jeu, c'est bien. Maman tape dans ses mains. Maya rit. Elles ajoutent un toit. Puis elles rangent les cubes. Maya a éteint. Elle a choisi un autre jeu.</t>
+          <t>La lampe du salon est déjà allumée. Le rideau est couleur miel. Un coussin garde une petite forme. Nina vit ici, avec maman. Papa range le linge, tout près. Dehors, le jour s'en va. En ce moment, un dessin brille. Les couleurs dansent sur l'écran. Nina est assise sur le tapis. Le tapis est doux, tout épais. Maman s'assoit près d'elle. Nina. Fini. Nina écoute. Elle va vers l'écran. Elle éteint. L'écran devient noir. Elle pose la télécommande. Bravo, Nina. Tu as éteint. On prend un autre jeu. Tu vas choisir ? Les cubes en bois. Les cubes sentent le bois. Ils sont lisses, un peu lourds. Nina pose un cube rouge. Maman pose un cube bleu. La tour grandit. Elle est haute ! Oui. Une belle tour. L'écran est éteint. Un autre jeu, c'est bien. L'écran est éteint. Bravo, Nina. Tu as fait du bon travail. Elles ajoutent un toit. Le toit est un cube jaune. Tu as entendu le petit bruit ? Oui. Le bois fait toc. La tour tient. Le salon est calme. On range les cubes ? Nina range un cube. Maman range la boîte. Merci, maman. Merci, Nina.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,16 +1325,61 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Maya est dans le salon. Elle regarde un dessin à l'écran. Les couleurs dansent. Maman s'assoit près d'elle.
-maman|Fini. L'adulte dit fini.
-narrateur|Maya écoute. Elle va éteindre. Maya éteint l'écran. L'écran devient noir. Elle pose la télécommande.
+          <t>narrateur|La lampe du salon est déjà allumée.
+narrateur|Le rideau est couleur miel.
+narrateur|Un coussin garde une petite forme.
+narrateur|Nina vit ici, avec maman.
+narrateur|Papa range le linge, tout près.
+narrateur|Dehors, le jour s'en va.
+narrateur|En ce moment, un dessin brille.
+narrateur|Les couleurs dansent sur l'écran.
+narrateur|Nina est assise sur le tapis.
+narrateur|Le tapis est doux, tout épais.
+narrateur|Maman s'assoit près d'elle.
+maman|Nina.
+maman|Fini.
+narrateur|Nina écoute.
+narrateur|Elle va vers l'écran.
+narrateur|Elle éteint.
+narrateur|L'écran devient noir.
+narrateur|Elle pose la télécommande.
+maman|Bravo, Nina.
+maman|Tu as éteint.
 maman|On prend un autre jeu.
-narrateur|Maya va choisir un jeu. Elle choisit les cubes en bois. Elles construisent une tour. La tour est haute.
+maman|Tu vas choisir ?
+enfant-f|Les cubes en bois.
+narrateur|Les cubes sentent le bois.
+narrateur|Ils sont lisses, un peu lourds.
+narrateur|Nina pose un cube rouge.
+narrateur|Maman pose un cube bleu.
+narrateur|La tour grandit.
+enfant-f|Elle est haute !
+maman|Oui.
+maman|Une belle tour.
+maman|L'écran est éteint.
+maman|Un autre jeu, c'est bien.
 enfant-f|L'écran est éteint.
-narrateur|Un autre jeu, c'est bien. Maman tape dans ses mains. Maya rit. Elles ajoutent un toit. Puis elles rangent les cubes. Maya a éteint. Elle a choisi un autre jeu.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+maman|Bravo, Nina.
+maman|Tu as fait du bon travail.
+narrateur|Elles ajoutent un toit.
+narrateur|Le toit est un cube jaune.
+maman|Tu as entendu le petit bruit ?
+enfant-f|Oui.
+enfant-f|Le bois fait toc.
+narrateur|La tour tient.
+narrateur|Le salon est calme.
+maman|On range les cubes ?
+narrateur|Nina range un cube.
+narrateur|Maman range la boîte.
+enfant-f|Merci, maman.
+maman|Merci, Nina.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>telecommande,cubes</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1346,7 +1404,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Maman dit fini. Que fait Maya ?</t>
+          <t>Maman dit fini. Que fait Nina ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1502,7 +1560,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Maman dit fini. Que fait Maya ?</t>
+          <t>narrateur|Maman dit fini.
+narrateur|Que fait Nina ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1530,7 +1589,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Maman a dit fini. Maya a éteint. Elle a pris un autre jeu. Les cubes, c'était bien.</t>
+          <t>Maman a dit fini. Nina a éteint. Elle a pris un autre jeu. Tu as éteint ? Oui, maman. J'ai pris les cubes. Bravo, Nina. Quand on dit fini, on éteint. Puis on prend un autre jeu. C'est du bon travail. Les cubes, c'était bien.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1674,7 +1733,17 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Maman a dit fini. Maya a éteint. Elle a pris un autre jeu. Les cubes, c'était bien.</t>
+          <t>narrateur|Maman a dit fini.
+narrateur|Nina a éteint.
+narrateur|Elle a pris un autre jeu.
+maman|Tu as éteint ?
+enfant-f|Oui, maman.
+enfant-f|J'ai pris les cubes.
+maman|Bravo, Nina.
+maman|Quand on dit fini, on éteint.
+maman|Puis on prend un autre jeu.
+maman|C'est du bon travail.
+narrateur|Les cubes, c'était bien.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1702,7 +1771,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>La tour reste un moment. Maya dit merci à maman. Le salon est calme.</t>
+          <t>La tour reste un moment. Le rideau est encore couleur miel. La lampe éclaire le tapis. Merci, maman. Merci, Nina. Le salon est calme. On reste encore un peu ? Oui. Nina touche un cube. Le bois est lisse. Tu as éteint. Tu as choisi un autre jeu. Bravo.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1838,7 +1907,19 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|La tour reste un moment. Maya dit merci à maman. Le salon est calme.</t>
+          <t>narrateur|La tour reste un moment.
+narrateur|Le rideau est encore couleur miel.
+narrateur|La lampe éclaire le tapis.
+enfant-f|Merci, maman.
+maman|Merci, Nina.
+maman|Le salon est calme.
+maman|On reste encore un peu ?
+enfant-f|Oui.
+narrateur|Nina touche un cube.
+narrateur|Le bois est lisse.
+maman|Tu as éteint.
+maman|Tu as choisi un autre jeu.
+maman|Bravo.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1866,7 +1947,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Maman a dit fini. J'ai éteint. On a joué aux cubes. Bravo. Tu as fait du bon travail. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2006,7 +2087,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|Maman a dit fini.
+enfant-f|J'ai éteint.
+enfant-f|On a joué aux cubes.
+maman|Bravo.
+maman|Tu as fait du bon travail.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2028,7 +2114,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2066,6 +2152,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.ECR.001-01.xlsx
+++ b/stories/arbres/ATOM-SAN.ECR.001-01.xlsx
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>La lampe du salon est déjà allumée. Le rideau est couleur miel. Un coussin garde une petite forme. Nina vit ici, avec maman. Papa range le linge, tout près. Dehors, le jour s'en va. En ce moment, un dessin brille. Les couleurs dansent sur l'écran. Nina est assise sur le tapis. Le tapis est doux, tout épais. Maman s'assoit près d'elle. Nina. Fini. Nina écoute. Elle va vers l'écran. Elle éteint. L'écran devient noir. Elle pose la télécommande. Bravo, Nina. Tu as éteint. On prend un autre jeu. Tu vas choisir ? Les cubes en bois. Les cubes sentent le bois. Ils sont lisses, un peu lourds. Nina pose un cube rouge. Maman pose un cube bleu. La tour grandit. Elle est haute ! Oui. Une belle tour. L'écran est éteint. Un autre jeu, c'est bien. L'écran est éteint. Bravo, Nina. Tu as fait du bon travail. Elles ajoutent un toit. Le toit est un cube jaune. Tu as entendu le petit bruit ? Oui. Le bois fait toc. La tour tient. Le salon est calme. On range les cubes ? Nina range un cube. Maman range la boîte. Merci, maman. Merci, Nina.</t>
+          <t>La lampe du salon est déjà allumée. Elle fait un rond jaune au plafond. Le rideau est couleur miel. Un coussin garde une petite forme. Nina vit ici, avec maman. Papa range le linge, tout près. Dehors, le jour s'en va. Un oiseau rentre dans l'arbre. Sur le tapis, un dessin brille. Les couleurs dansent sur l'écran. Nina est assise. Le tapis est doux, tout épais. Ses pieds sont dans les poils. Maman s'assoit près d'elle. Nina. Fini. Nina écoute. Elle va vers l'écran. Elle éteint. L'écran devient noir. Elle pose la télécommande. Bravo, Nina. Tu as éteint. On prend un autre jeu. Tu vas choisir ? Les cubes en bois. Les cubes sentent le bois. Ils sont lisses, un peu lourds. Nina pose un cube rouge. Maman pose un cube bleu. Toc. La tour grandit. Tu as vu le cube jaune ? Il brille un peu. Elle est haute ! Oui. Une belle tour. L'écran est éteint. Un autre jeu, c'est bien. L'écran est éteint. Bravo, Nina. Elles ajoutent un toit. Le toit est un cube jaune. Tu as entendu le petit bruit ? Oui. Le bois fait toc. La tour tient. Le salon est calme. On range les cubes ? Nina range un cube. Maman range la boîte. Merci, maman. Merci, Nina.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Maya est dans le salon. Elle regarde un dessin à l'écran. Les couleurs dansent. Maman s'assoit près d'elle. Maman dit : fini. L'adulte dit fini. Maya écoute. Elle va &lt;emphasis level="moderate"&gt;éteindre&lt;/emphasis&gt;. Maya éteint l'écran. L'écran devient noir. Elle pose la télécommande. Maman dit : on prend un autre jeu. Maya va choisir un jeu. Elle choisit les cubes en bois. Elles construisent une tour. La tour est haute. Maya dit : l'écran est éteint. Un autre jeu, c'est bien. Maman tape dans ses mains. Maya rit. Elles ajoutent un toit. Puis elles rangent les cubes. Maya a éteint. Elle a choisi un autre jeu.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>La lampe du salon est déjà allumée. Elle fait un rond jaune au plafond. Le rideau est couleur miel. Un coussin garde une petite forme. Nina vit ici, avec maman. Papa range le linge, tout près. Dehors, le jour s'en va. Un oiseau rentre dans l'arbre. Sur le tapis, un dessin brille. Les couleurs dansent sur l'écran. Nina est assise. Le tapis est doux, tout épais. Ses pieds sont dans les poils. Maman s'assoit près d'elle. Nina. Fini. Nina écoute. Elle va vers l'écran. Elle éteint. L'écran devient noir. Elle pose la télécommande. Bravo, Nina. Tu as éteint. On prend un autre jeu. Tu vas choisir ? Les cubes en bois. Les cubes sentent le bois. Ils sont lisses, un peu lourds. Nina pose un cube rouge. Maman pose un cube bleu. Toc. La tour grandit. Tu as vu le cube jaune ? Il brille un peu. Elle est haute ! Oui. Une belle tour. L'écran est éteint. Un autre jeu, c'est bien. L'écran est éteint. Bravo, Nina. Elles ajoutent un toit. Le toit est un cube jaune. Tu as entendu le petit bruit ? Oui. Le bois fait toc. La tour tient. Le salon est calme. On range les cubes ? Nina range un cube. Maman range la boîte. Merci, maman. Merci, Nina.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1326,15 +1326,18 @@
       <c r="AW2" t="inlineStr">
         <is>
           <t>narrateur|La lampe du salon est déjà allumée.
+narrateur|Elle fait un rond jaune au plafond.
 narrateur|Le rideau est couleur miel.
 narrateur|Un coussin garde une petite forme.
 narrateur|Nina vit ici, avec maman.
 narrateur|Papa range le linge, tout près.
 narrateur|Dehors, le jour s'en va.
-narrateur|En ce moment, un dessin brille.
+narrateur|Un oiseau rentre dans l'arbre.
+narrateur|Sur le tapis, un dessin brille.
 narrateur|Les couleurs dansent sur l'écran.
-narrateur|Nina est assise sur le tapis.
+narrateur|Nina est assise.
 narrateur|Le tapis est doux, tout épais.
+narrateur|Ses pieds sont dans les poils.
 narrateur|Maman s'assoit près d'elle.
 maman|Nina.
 maman|Fini.
@@ -1352,7 +1355,10 @@
 narrateur|Ils sont lisses, un peu lourds.
 narrateur|Nina pose un cube rouge.
 narrateur|Maman pose un cube bleu.
+narrateur|Toc.
 narrateur|La tour grandit.
+maman|Tu as vu le cube jaune ?
+enfant-f|Il brille un peu.
 enfant-f|Elle est haute !
 maman|Oui.
 maman|Une belle tour.
@@ -1360,7 +1366,6 @@
 maman|Un autre jeu, c'est bien.
 enfant-f|L'écran est éteint.
 maman|Bravo, Nina.
-maman|Tu as fait du bon travail.
 narrateur|Elles ajoutent un toit.
 narrateur|Le toit est un cube jaune.
 maman|Tu as entendu le petit bruit ?
@@ -1409,7 +1414,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Maman dit fini. Que fait Maya ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Maman dit fini. Que fait Nina ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1564,7 +1569,6 @@
 narrateur|Que fait Nina ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1589,12 +1593,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Maman a dit fini. Nina a éteint. Elle a pris un autre jeu. Tu as éteint ? Oui, maman. J'ai pris les cubes. Bravo, Nina. Quand on dit fini, on éteint. Puis on prend un autre jeu. C'est du bon travail. Les cubes, c'était bien.</t>
+          <t>Maman a dit fini. Nina a éteint. Elle a pris un autre jeu. Tu as éteint ? Oui, maman. J'ai pris les cubes. Bravo, Nina. Quand on dit fini, on éteint. Puis on prend un autre jeu. Les cubes, c'était bien.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Maman a dit fini. Maya a éteint. Elle a pris un &lt;emphasis level="moderate"&gt;autre&lt;/emphasis&gt; jeu. Les cubes, c'était bien.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Maman a dit fini. Nina a éteint. Elle a pris un autre jeu. Tu as éteint ? Oui, maman. J'ai pris les cubes. Bravo, Nina. Quand on dit fini, on éteint. Puis on prend un autre jeu. Les cubes, c'était bien.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1742,11 +1746,9 @@
 maman|Bravo, Nina.
 maman|Quand on dit fini, on éteint.
 maman|Puis on prend un autre jeu.
-maman|C'est du bon travail.
 narrateur|Les cubes, c'était bien.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1771,12 +1773,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>La tour reste un moment. Le rideau est encore couleur miel. La lampe éclaire le tapis. Merci, maman. Merci, Nina. Le salon est calme. On reste encore un peu ? Oui. Nina touche un cube. Le bois est lisse. Tu as éteint. Tu as choisi un autre jeu. Bravo.</t>
+          <t>La tour reste un moment. Le rideau est encore couleur miel. La lampe éclaire le tapis. Merci, maman. Merci, Nina. Le salon est calme. On reste encore un peu ? Oui. Nina touche un cube. Le bois est lisse. La tour attend. Bravo.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;La tour reste un moment. Maya dit merci à maman. Le salon est calme.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>La tour reste un moment. Le rideau est encore couleur miel. La lampe éclaire le tapis. Merci, maman. Merci, Nina. Le salon est calme. On reste encore un peu ? Oui. Nina touche un cube. Le bois est lisse. La tour attend. Bravo.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1917,12 +1919,10 @@
 enfant-f|Oui.
 narrateur|Nina touche un cube.
 narrateur|Le bois est lisse.
-maman|Tu as éteint.
-maman|Tu as choisi un autre jeu.
+maman|La tour attend.
 maman|Bravo.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1947,12 +1947,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Maman a dit fini. J'ai éteint. On a joué aux cubes. Bravo. Tu as fait du bon travail. L'histoire est finie.</t>
+          <t>Maman a dit fini. J'ai éteint. On a joué aux cubes. Bravo.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Maman a dit fini. J'ai éteint. On a joué aux cubes. Bravo.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2090,12 +2090,9 @@
           <t>enfant-f|Maman a dit fini.
 enfant-f|J'ai éteint.
 enfant-f|On a joué aux cubes.
-maman|Bravo.
-maman|Tu as fait du bon travail.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+maman|Bravo.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2114,7 +2111,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2159,6 +2156,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.ECR.001-01.xlsx
+++ b/stories/arbres/ATOM-SAN.ECR.001-01.xlsx
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -684,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Maya, maman</t>
+          <t>Nina, maman</t>
         </is>
       </c>
     </row>
